--- a/00 dsa-sheet-materials/01 DSA Naqeem.xlsx
+++ b/00 dsa-sheet-materials/01 DSA Naqeem.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/NaqeemMomin/Documents/frontend-technologies/Training/front-end-dsa/00 DSA-sheet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/NaqeemMomin/Documents/Development/05 dsa-with-javascript/00 dsa-sheet-materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E82A91-373C-3B49-A73A-92A3A10E562C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437981DF-8785-2143-96A6-72D1748F01E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/00 dsa-sheet-materials/01 DSA Naqeem.xlsx
+++ b/00 dsa-sheet-materials/01 DSA Naqeem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/NaqeemMomin/Documents/Development/05 dsa-with-javascript/00 dsa-sheet-materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437981DF-8785-2143-96A6-72D1748F01E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63359326-2149-5344-A85B-B0195A382B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
